--- a/data/department_schedules_finals/Bilgisayar Mühendisliği.xlsx
+++ b/data/department_schedules_finals/Bilgisayar Mühendisliği.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ercx2\Desktop\Scheduling Theory_02\Paper\scheduling\Campus-Scheduling\data\department_schedules_finals\modified\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/9e402f802124af4b/Masaüstü/Projects/Campus-Scheduling/data/department_schedules_finals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF7561C-D761-4C9F-9C22-0F80AFA6642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{DAF7561C-D761-4C9F-9C22-0F80AFA6642F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8CDEFCC0-4388-4EF3-9069-B3B3D57502A0}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="20760" yWindow="-21720" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="87">
   <si>
     <t>Year:</t>
   </si>
@@ -224,6 +224,63 @@
   </si>
   <si>
     <t>Rooms Used</t>
+  </si>
+  <si>
+    <t>CAD1,YLAB 1,YLAB 2,YLAB 3</t>
+  </si>
+  <si>
+    <t>D206</t>
+  </si>
+  <si>
+    <t>YLAB 1,YLAB 2</t>
+  </si>
+  <si>
+    <t>Amfi 3,BB01,BB04,D205,D206</t>
+  </si>
+  <si>
+    <t>Amfi 3,Amfi 4,BB01,BB04,BZ01</t>
+  </si>
+  <si>
+    <t>Amfi 3,Amfi 4,BB01,BZ01,D205</t>
+  </si>
+  <si>
+    <t>D205,D206</t>
+  </si>
+  <si>
+    <t>BZ01,D205,D206,BB01</t>
+  </si>
+  <si>
+    <t>YLAB 1,YLAB 2,YLAB 3,CAD1</t>
+  </si>
+  <si>
+    <t>Amfi 4,BB01</t>
+  </si>
+  <si>
+    <t>D205,D206,BZ01,BB04</t>
+  </si>
+  <si>
+    <t>D205</t>
+  </si>
+  <si>
+    <t>YLAB 1,YLAB 2,CAD1</t>
+  </si>
+  <si>
+    <t>BB04,BZ01</t>
+  </si>
+  <si>
+    <t>D206,BB04,YLAB 1,YLAB 2</t>
+  </si>
+  <si>
+    <t>YLAB 1</t>
+  </si>
+  <si>
+    <t>D206,D205</t>
+  </si>
+  <si>
+    <t>YLAB 2</t>
+  </si>
+  <si>
+    <t>Amfi 3</t>
   </si>
 </sst>
 </file>
@@ -330,6 +387,38 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
       <font>
         <b/>
         <i val="0"/>
@@ -358,38 +447,6 @@
         <bottom/>
       </border>
     </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -403,16 +460,20 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6D804807-F4DB-4641-8868-3C8B7E6F974D}" name="Table1" displayName="Table1" ref="A1:F32" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0" headerRowBorderDxfId="9" tableBorderDxfId="8">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{6D804807-F4DB-4641-8868-3C8B7E6F974D}" name="Table1" displayName="Table1" ref="A1:F32" totalsRowShown="0" headerRowDxfId="9" dataDxfId="7" headerRowBorderDxfId="8" tableBorderDxfId="6">
   <autoFilter ref="A1:F32" xr:uid="{6D804807-F4DB-4641-8868-3C8B7E6F974D}"/>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{4F6755EA-FE75-4698-97BF-3B64D2FD363A}" name="Year:" dataDxfId="7"/>
-    <tableColumn id="2" xr3:uid="{4E63F23B-EBE0-4620-BC58-4A3F5174E8B8}" name="Course ID" dataDxfId="6"/>
-    <tableColumn id="3" xr3:uid="{946DD1D7-53D2-4566-8E9F-3E76FEAF849C}" name="Date" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{B34557C0-D930-44D9-A811-D5F01B299ECF}" name="Rooms" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{C09534FA-04D2-48E5-8497-0DB03EB02FC5}" name="Course Name" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{C7781146-3CF4-4B66-B0B2-F7C86896AE17}" name="Rooms Used" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{4F6755EA-FE75-4698-97BF-3B64D2FD363A}" name="Year:" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4E63F23B-EBE0-4620-BC58-4A3F5174E8B8}" name="Course ID" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{946DD1D7-53D2-4566-8E9F-3E76FEAF849C}" name="Date" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{B34557C0-D930-44D9-A811-D5F01B299ECF}" name="Rooms" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{C09534FA-04D2-48E5-8497-0DB03EB02FC5}" name="Course Name" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{C7781146-3CF4-4B66-B0B2-F7C86896AE17}" name="Rooms Used" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -706,14 +767,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="2" max="2" width="10.90625" customWidth="1"/>
-    <col min="5" max="5" width="35.26953125" customWidth="1"/>
-    <col min="6" max="6" width="56.36328125" customWidth="1"/>
+    <col min="2" max="2" width="10.9296875" customWidth="1"/>
+    <col min="5" max="5" width="35.265625" customWidth="1"/>
+    <col min="6" max="6" width="56.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -733,7 +794,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A2" s="2">
         <v>1</v>
       </c>
@@ -749,9 +810,11 @@
       <c r="E2" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F2" s="2"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F2" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -767,9 +830,11 @@
       <c r="E3" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F3" s="2"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F3" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A4" s="2">
         <v>1</v>
       </c>
@@ -785,9 +850,11 @@
       <c r="E4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="F4" s="2"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F4" s="2" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A5" s="2">
         <v>1</v>
       </c>
@@ -803,9 +870,11 @@
       <c r="E5" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="F5" s="2"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A6" s="2">
         <v>1</v>
       </c>
@@ -821,9 +890,11 @@
       <c r="E6" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="F6" s="2"/>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A7" s="2">
         <v>1</v>
       </c>
@@ -839,9 +910,11 @@
       <c r="E7" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="F7" s="2"/>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F7" s="2" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A8" s="2">
         <v>1</v>
       </c>
@@ -857,9 +930,11 @@
       <c r="E8" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="F8" s="2"/>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F8" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A9" s="2">
         <v>1</v>
       </c>
@@ -875,9 +950,11 @@
       <c r="E9" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="2"/>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F9" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A10" s="3">
         <v>2</v>
       </c>
@@ -893,9 +970,11 @@
       <c r="E10" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="F10" s="3"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F10" s="3" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A11" s="3">
         <v>2</v>
       </c>
@@ -911,9 +990,11 @@
       <c r="E11" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="F11" s="3"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F11" s="3" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A12" s="3">
         <v>2</v>
       </c>
@@ -929,9 +1010,11 @@
       <c r="E12" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="3"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F12" s="3" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A13" s="3">
         <v>2</v>
       </c>
@@ -947,9 +1030,11 @@
       <c r="E13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="3"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F13" s="3" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A14" s="3">
         <v>2</v>
       </c>
@@ -965,9 +1050,11 @@
       <c r="E14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F14" s="3" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A15" s="4">
         <v>3</v>
       </c>
@@ -983,9 +1070,11 @@
       <c r="E15" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="4"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F15" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A16" s="4">
         <v>3</v>
       </c>
@@ -1001,9 +1090,11 @@
       <c r="E16" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="F16" s="4"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F16" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A17" s="4">
         <v>3</v>
       </c>
@@ -1019,9 +1110,11 @@
       <c r="E17" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F17" s="4"/>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F17" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A18" s="4">
         <v>3</v>
       </c>
@@ -1037,9 +1130,11 @@
       <c r="E18" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="F18" s="4"/>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F18" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A19" s="4">
         <v>3</v>
       </c>
@@ -1055,9 +1150,11 @@
       <c r="E19" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="F19" s="4"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F19" s="4" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A20" s="4">
         <v>3</v>
       </c>
@@ -1073,9 +1170,11 @@
       <c r="E20" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="F20" s="4"/>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F20" s="4" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A21" s="4">
         <v>3</v>
       </c>
@@ -1091,9 +1190,11 @@
       <c r="E21" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="F21" s="4"/>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F21" s="4" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A22" s="4">
         <v>3</v>
       </c>
@@ -1109,9 +1210,11 @@
       <c r="E22" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="F22" s="4"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F22" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A23" s="4">
         <v>3</v>
       </c>
@@ -1127,9 +1230,11 @@
       <c r="E23" s="4" t="s">
         <v>57</v>
       </c>
-      <c r="F23" s="4"/>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F23" s="4" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A24" s="5">
         <v>4</v>
       </c>
@@ -1145,9 +1250,11 @@
       <c r="E24" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="F24" s="5"/>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F24" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A25" s="5">
         <v>4</v>
       </c>
@@ -1163,9 +1270,11 @@
       <c r="E25" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F25" s="5"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F25" s="5" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A26" s="5">
         <v>4</v>
       </c>
@@ -1181,9 +1290,11 @@
       <c r="E26" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="F26" s="5"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F26" s="5" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A27" s="5">
         <v>4</v>
       </c>
@@ -1199,9 +1310,11 @@
       <c r="E27" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F27" s="5"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F27" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A28" s="5">
         <v>4</v>
       </c>
@@ -1217,9 +1330,11 @@
       <c r="E28" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="F28" s="5"/>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F28" s="5" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A29" s="5">
         <v>4</v>
       </c>
@@ -1235,9 +1350,11 @@
       <c r="E29" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="F29" s="5"/>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F29" s="5" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A30" s="5">
         <v>4</v>
       </c>
@@ -1253,9 +1370,11 @@
       <c r="E30" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="F30" s="5"/>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F30" s="5" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A31" s="5">
         <v>4</v>
       </c>
@@ -1271,9 +1390,11 @@
       <c r="E31" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="F31" s="5"/>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="F31" s="5" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.45">
       <c r="A32" s="5">
         <v>4</v>
       </c>
@@ -1289,7 +1410,9 @@
       <c r="E32" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F32" s="5"/>
+      <c r="F32" s="5" t="s">
+        <v>86</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
